--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-15T10:13:43+00:00</t>
+    <t>2023-12-15T15:13:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-15T15:13:16+00:00</t>
+    <t>2023-12-16T04:14:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-16T04:14:56+00:00</t>
+    <t>2023-12-16T10:12:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-16T10:12:57+00:00</t>
+    <t>2023-12-16T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-16T15:11:58+00:00</t>
+    <t>2023-12-17T04:15:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-17T04:15:28+00:00</t>
+    <t>2023-12-17T10:12:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-17T10:12:19+00:00</t>
+    <t>2023-12-17T15:11:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-17T15:11:55+00:00</t>
+    <t>2023-12-18T04:15:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-18T04:15:56+00:00</t>
+    <t>2023-12-18T10:14:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-18T10:14:43+00:00</t>
+    <t>2023-12-18T15:13:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-18T15:13:16+00:00</t>
+    <t>2023-12-19T04:15:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T04:15:07+00:00</t>
+    <t>2023-12-19T10:13:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T10:13:14+00:00</t>
+    <t>2023-12-19T15:12:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T15:12:47+00:00</t>
+    <t>2023-12-20T10:11:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-20T10:11:26+00:00</t>
+    <t>2023-12-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-20T15:11:12+00:00</t>
+    <t>2023-12-21T04:15:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T04:15:05+00:00</t>
+    <t>2023-12-21T10:13:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T10:13:12+00:00</t>
+    <t>2023-12-21T15:12:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T15:12:28+00:00</t>
+    <t>2023-12-22T04:14:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-22T04:14:47+00:00</t>
+    <t>2023-12-22T10:13:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-22T10:13:22+00:00</t>
+    <t>2023-12-22T15:12:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-22T15:12:35+00:00</t>
+    <t>2023-12-23T04:14:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-23T04:14:21+00:00</t>
+    <t>2023-12-23T10:12:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-23T10:12:00+00:00</t>
+    <t>2023-12-23T15:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-23T15:11:50+00:00</t>
+    <t>2023-12-24T04:14:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-24T04:14:34+00:00</t>
+    <t>2023-12-24T10:12:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-24T10:12:10+00:00</t>
+    <t>2023-12-24T15:11:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-24T15:11:47+00:00</t>
+    <t>2023-12-25T04:14:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-25T04:14:59+00:00</t>
+    <t>2023-12-25T15:13:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-25T15:13:20+00:00</t>
+    <t>2023-12-26T04:15:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-26T04:15:03+00:00</t>
+    <t>2023-12-26T10:13:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-26T10:13:11+00:00</t>
+    <t>2023-12-26T15:12:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-26T15:12:21+00:00</t>
+    <t>2023-12-28T04:15:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T04:15:03+00:00</t>
+    <t>2023-12-28T10:13:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T10:13:53+00:00</t>
+    <t>2023-12-28T15:13:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T15:13:05+00:00</t>
+    <t>2023-12-29T04:15:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T04:15:13+00:00</t>
+    <t>2023-12-29T10:13:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T10:13:25+00:00</t>
+    <t>2023-12-29T15:12:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T15:12:02+00:00</t>
+    <t>2023-12-30T04:15:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-30T04:15:40+00:00</t>
+    <t>2023-12-30T10:12:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-30T10:12:29+00:00</t>
+    <t>2023-12-30T15:11:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-30T15:11:59+00:00</t>
+    <t>2023-12-31T04:14:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-31T04:14:35+00:00</t>
+    <t>2023-12-31T10:12:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-31T10:12:20+00:00</t>
+    <t>2023-12-31T15:11:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-31T15:11:53+00:00</t>
+    <t>2024-01-01T04:15:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-01T04:15:30+00:00</t>
+    <t>2024-01-01T10:13:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-01T10:13:45+00:00</t>
+    <t>2024-01-01T15:12:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-01T15:12:10+00:00</t>
+    <t>2024-01-02T04:14:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-02T04:14:47+00:00</t>
+    <t>2024-01-02T10:13:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-02T10:13:08+00:00</t>
+    <t>2024-01-02T15:12:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-02T15:12:57+00:00</t>
+    <t>2024-01-03T04:15:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-03T04:15:04+00:00</t>
+    <t>2024-01-03T10:13:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-03T10:13:16+00:00</t>
+    <t>2024-01-03T15:12:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-03T15:12:21+00:00</t>
+    <t>2024-01-04T04:14:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-04T04:14:37+00:00</t>
+    <t>2024-01-04T10:13:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-04T10:13:28+00:00</t>
+    <t>2024-01-04T15:14:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-04T15:14:06+00:00</t>
+    <t>2024-01-05T04:15:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-05T04:15:12+00:00</t>
+    <t>2024-01-05T10:13:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-05T10:13:28+00:00</t>
+    <t>2024-01-05T15:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-05T15:13:15+00:00</t>
+    <t>2024-01-06T04:14:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-06T04:14:41+00:00</t>
+    <t>2024-01-06T10:12:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-06T10:12:10+00:00</t>
+    <t>2024-01-06T15:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-06T15:11:50+00:00</t>
+    <t>2024-01-08T04:16:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-08T04:16:08+00:00</t>
+    <t>2024-01-08T10:14:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-08T10:14:14+00:00</t>
+    <t>2024-01-09T04:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-09T04:15:57+00:00</t>
+    <t>2024-01-09T10:13:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-09T10:13:51+00:00</t>
+    <t>2024-01-09T15:13:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-09T15:13:08+00:00</t>
+    <t>2024-01-10T04:15:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-10T04:15:17+00:00</t>
+    <t>2024-01-10T10:13:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-10T10:13:17+00:00</t>
+    <t>2024-01-10T15:12:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-10T15:12:51+00:00</t>
+    <t>2024-01-11T04:15:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-11T04:15:35+00:00</t>
+    <t>2024-01-11T10:13:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-11T10:13:36+00:00</t>
+    <t>2024-01-11T15:13:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-11T15:13:05+00:00</t>
+    <t>2024-01-12T04:16:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-12T04:16:04+00:00</t>
+    <t>2024-01-12T10:13:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-12T10:13:42+00:00</t>
+    <t>2024-01-12T15:12:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-12T15:12:39+00:00</t>
+    <t>2024-01-13T04:15:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T04:15:17+00:00</t>
+    <t>2024-01-13T10:12:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T10:12:09+00:00</t>
+    <t>2024-01-13T15:12:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T15:12:12+00:00</t>
+    <t>2024-01-14T04:15:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T04:15:07+00:00</t>
+    <t>2024-01-14T10:13:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T10:13:00+00:00</t>
+    <t>2024-01-14T15:12:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T15:12:46+00:00</t>
+    <t>2024-01-15T04:16:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-15T04:16:08+00:00</t>
+    <t>2024-01-15T10:14:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-15T10:14:35+00:00</t>
+    <t>2024-01-15T15:13:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-15T15:13:20+00:00</t>
+    <t>2024-01-16T04:15:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-16T04:15:29+00:00</t>
+    <t>2024-01-16T10:13:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-16T10:13:47+00:00</t>
+    <t>2024-01-16T15:13:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-16T15:13:25+00:00</t>
+    <t>2024-01-17T04:15:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-17T04:15:56+00:00</t>
+    <t>2024-01-17T10:13:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-17T10:13:45+00:00</t>
+    <t>2024-01-17T15:13:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-17T15:13:25+00:00</t>
+    <t>2024-01-18T04:15:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-18T04:15:29+00:00</t>
+    <t>2024-01-18T10:15:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-18T10:15:26+00:00</t>
+    <t>2024-01-18T15:13:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-18T15:13:28+00:00</t>
+    <t>2024-01-19T04:15:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-19T04:15:25+00:00</t>
+    <t>2024-01-19T10:13:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-19T10:13:45+00:00</t>
+    <t>2024-01-19T15:13:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-19T15:13:27+00:00</t>
+    <t>2024-01-20T04:14:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-20T04:14:50+00:00</t>
+    <t>2024-01-20T10:12:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-20T10:12:15+00:00</t>
+    <t>2024-01-20T15:12:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-20T15:12:22+00:00</t>
+    <t>2024-01-21T04:15:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-21T04:15:25+00:00</t>
+    <t>2024-01-21T10:12:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-21T10:12:51+00:00</t>
+    <t>2024-01-21T15:11:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-21T15:11:52+00:00</t>
+    <t>2024-01-22T04:15:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-22T04:15:52+00:00</t>
+    <t>2024-01-22T10:14:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-22T10:14:14+00:00</t>
+    <t>2024-01-22T15:13:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-22T15:13:54+00:00</t>
+    <t>2024-01-23T04:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-23T04:15:47+00:00</t>
+    <t>2024-01-23T10:14:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-23T10:14:06+00:00</t>
+    <t>2024-01-23T15:13:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-23T15:13:43+00:00</t>
+    <t>2024-01-24T04:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-24T04:16:05+00:00</t>
+    <t>2024-01-24T10:13:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-cladimed-valueset.xlsx
+++ b/ig/main/ValueSet-cladimed-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-24T10:13:46+00:00</t>
+    <t>2024-01-24T15:13:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
